--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task064.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task064.xlsx
@@ -100,13 +100,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="14.85546875" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="4" max="4" width="10" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="9.5703125" customWidth="true"/>
     <col min="6" max="6" width="16.140625" customWidth="true"/>
     <col min="7" max="7" width="20.85546875" customWidth="true"/>
@@ -207,6 +207,94 @@
         <v>5.2527870174817721</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>317</v>
+      </c>
+      <c r="B3" s="0">
+        <v>254</v>
+      </c>
+      <c r="C3" s="0">
+        <v>317</v>
+      </c>
+      <c r="D3" s="0">
+        <v>93.412340928608273</v>
+      </c>
+      <c r="E3" s="0">
+        <v>471.15000000000003</v>
+      </c>
+      <c r="F3" s="0">
+        <v>156.32302276034568</v>
+      </c>
+      <c r="G3" s="0">
+        <v>6768.6261394581488</v>
+      </c>
+      <c r="H3" s="0">
+        <v>-1797.6842944480468</v>
+      </c>
+      <c r="I3" s="0">
+        <v>5.7850000000000001</v>
+      </c>
+      <c r="J3" s="0">
+        <v>15.115</v>
+      </c>
+      <c r="K3" s="0">
+        <v>2.3900000000000006</v>
+      </c>
+      <c r="L3" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M3" s="0">
+        <v>264.09827946044732</v>
+      </c>
+      <c r="N3" s="0">
+        <v>5.2527870174817721</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>317</v>
+      </c>
+      <c r="B4" s="0">
+        <v>255</v>
+      </c>
+      <c r="C4" s="0">
+        <v>317</v>
+      </c>
+      <c r="D4" s="0">
+        <v>93.412340928608273</v>
+      </c>
+      <c r="E4" s="0">
+        <v>471.15000000000003</v>
+      </c>
+      <c r="F4" s="0">
+        <v>156.32302276034568</v>
+      </c>
+      <c r="G4" s="0">
+        <v>6768.6261394581488</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-1797.6842944480468</v>
+      </c>
+      <c r="I4" s="0">
+        <v>5.7850000000000001</v>
+      </c>
+      <c r="J4" s="0">
+        <v>15.115</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.3900000000000006</v>
+      </c>
+      <c r="L4" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M4" s="0">
+        <v>264.09827946044732</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.2527870174817721</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task064.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G2_task064.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -295,6 +295,50 @@
         <v>5.2527870174817721</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>317</v>
+      </c>
+      <c r="B5" s="0">
+        <v>256</v>
+      </c>
+      <c r="C5" s="0">
+        <v>317</v>
+      </c>
+      <c r="D5" s="0">
+        <v>93.412340928608273</v>
+      </c>
+      <c r="E5" s="0">
+        <v>471.15000000000003</v>
+      </c>
+      <c r="F5" s="0">
+        <v>156.32302276034568</v>
+      </c>
+      <c r="G5" s="0">
+        <v>6768.6261394581488</v>
+      </c>
+      <c r="H5" s="0">
+        <v>-1797.6842944480468</v>
+      </c>
+      <c r="I5" s="0">
+        <v>5.7850000000000001</v>
+      </c>
+      <c r="J5" s="0">
+        <v>15.115</v>
+      </c>
+      <c r="K5" s="0">
+        <v>2.3900000000000006</v>
+      </c>
+      <c r="L5" s="0">
+        <v>3.4650000000000003</v>
+      </c>
+      <c r="M5" s="0">
+        <v>264.09827946044732</v>
+      </c>
+      <c r="N5" s="0">
+        <v>5.2527870174817721</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>